--- a/Inputs/Tables/PECs_and_Targets_with_FeS_cofactor.xlsx
+++ b/Inputs/Tables/PECs_and_Targets_with_FeS_cofactor.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aliyashilanova/Downloads/IRP_my_repo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aliyashilanova/Downloads/IRP_my_repo/IRP_PEC_Target_Redox_Analysis/Inputs/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E54D173B-FC9F-1C47-B103-89C1BB78D8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93B0E94-686E-DB4B-9218-CCB8D18D2965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="460" yWindow="500" windowWidth="27640" windowHeight="16440" xr2:uid="{DC87B68A-B6FD-2F42-80C0-F1DBED6135F1}"/>
   </bookViews>
@@ -2165,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B47B1EA-AF5D-9E4B-A4BA-A203E99E08B6}">
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:J96"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -3057,7 +3057,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>0</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>0</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -3144,7 +3144,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>0</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>0</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>0</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>0</v>
       </c>
@@ -3285,11 +3285,8 @@
       <c r="I40" t="s">
         <v>253</v>
       </c>
-      <c r="K40">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>0</v>
       </c>
@@ -3318,7 +3315,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>0</v>
       </c>
@@ -3347,7 +3344,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>0</v>
       </c>
@@ -3376,7 +3373,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>0</v>
       </c>
@@ -3405,7 +3402,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>0</v>
       </c>
@@ -3434,7 +3431,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>0</v>
       </c>
@@ -3463,7 +3460,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>0</v>
       </c>
@@ -3489,7 +3486,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>0</v>
       </c>
